--- a/public/sap-reporting/expansion-150-downloads/EXT-FI23-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI23-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R80956c65c47745b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R239fcb15b12443a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R80ef1ad613794c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rec7840d8d82d481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Re3b33f4d162f4fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R8bb64647ad0c4e72"/>
   </x:sheets>
 </x:workbook>
 </file>
